--- a/filo.xlsx
+++ b/filo.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\users\i_cevik1\Desktop\İSMAİL HAKKI ÇEVİK\AMM Finder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\users\i_cevik1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38050EB8-5B58-47B7-BBE8-71A5C8F5BC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3B245B-E8E6-4474-8F94-576B0106AB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="THY Filo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'THY Filo'!$A$1:$E$536</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="585">
   <si>
     <t>MSN</t>
   </si>
@@ -906,15 +906,6 @@
     <t>TC-LRI</t>
   </si>
   <si>
-    <t>D-AYAL</t>
-  </si>
-  <si>
-    <t>D-AXXQ</t>
-  </si>
-  <si>
-    <t>D-AZYF</t>
-  </si>
-  <si>
     <t>319-133</t>
   </si>
   <si>
@@ -1054,6 +1045,747 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>777-3F2ER</t>
+  </si>
+  <si>
+    <t>TC-JJE</t>
+  </si>
+  <si>
+    <t>TC-JJF</t>
+  </si>
+  <si>
+    <t>TC-JJG</t>
+  </si>
+  <si>
+    <t>TC-JJH</t>
+  </si>
+  <si>
+    <t>TC-JJI</t>
+  </si>
+  <si>
+    <t>TC-JJJ</t>
+  </si>
+  <si>
+    <t>TC-JJK</t>
+  </si>
+  <si>
+    <t>TC-JJL</t>
+  </si>
+  <si>
+    <t>TC-JJM</t>
+  </si>
+  <si>
+    <t>TC-JJN</t>
+  </si>
+  <si>
+    <t>TC-JJO</t>
+  </si>
+  <si>
+    <t>TC-JJP</t>
+  </si>
+  <si>
+    <t>TC-JJR</t>
+  </si>
+  <si>
+    <t>TC-JJS</t>
+  </si>
+  <si>
+    <t>TC-JJT</t>
+  </si>
+  <si>
+    <t>TC-JJU</t>
+  </si>
+  <si>
+    <t>TC-JJV</t>
+  </si>
+  <si>
+    <t>TC-JJY</t>
+  </si>
+  <si>
+    <t>TC-JJZ</t>
+  </si>
+  <si>
+    <t>TC-LJA</t>
+  </si>
+  <si>
+    <t>TC-LJB</t>
+  </si>
+  <si>
+    <t>TC-LJC</t>
+  </si>
+  <si>
+    <t>TC-LJD</t>
+  </si>
+  <si>
+    <t>TC-LJE</t>
+  </si>
+  <si>
+    <t>TC-LJF</t>
+  </si>
+  <si>
+    <t>TC-LJG</t>
+  </si>
+  <si>
+    <t>TC-LJH</t>
+  </si>
+  <si>
+    <t>TC-LJI</t>
+  </si>
+  <si>
+    <t>TC-LJJ</t>
+  </si>
+  <si>
+    <t>TC-LJK</t>
+  </si>
+  <si>
+    <t>777-36NER</t>
+  </si>
+  <si>
+    <t>TC-LKB</t>
+  </si>
+  <si>
+    <t>777-3U8ER</t>
+  </si>
+  <si>
+    <t>777-FF2F</t>
+  </si>
+  <si>
+    <t>TC-LJL</t>
+  </si>
+  <si>
+    <t>TC-LJM</t>
+  </si>
+  <si>
+    <t>TC-LJN</t>
+  </si>
+  <si>
+    <t>777-FF</t>
+  </si>
+  <si>
+    <t>TC-LJO</t>
+  </si>
+  <si>
+    <t>TC-LJP</t>
+  </si>
+  <si>
+    <t>TC-LJR</t>
+  </si>
+  <si>
+    <t>TC-LJS</t>
+  </si>
+  <si>
+    <t>TC-LJT</t>
+  </si>
+  <si>
+    <t>777-3Q8ER</t>
+  </si>
+  <si>
+    <t>TC-LKD</t>
+  </si>
+  <si>
+    <t>777-31HER</t>
+  </si>
+  <si>
+    <t>TC-LKE</t>
+  </si>
+  <si>
+    <t>TC-LKF</t>
+  </si>
+  <si>
+    <t>TC-LJV</t>
+  </si>
+  <si>
+    <t>TC-LJY</t>
+  </si>
+  <si>
+    <t>TC-LJZ</t>
+  </si>
+  <si>
+    <t>TC-LJU</t>
+  </si>
+  <si>
+    <t>737-8F2</t>
+  </si>
+  <si>
+    <t>TC-JFC</t>
+  </si>
+  <si>
+    <t>TC-JFD</t>
+  </si>
+  <si>
+    <t>TC-JFE</t>
+  </si>
+  <si>
+    <t>TC-JFF</t>
+  </si>
+  <si>
+    <t>TC-JFG</t>
+  </si>
+  <si>
+    <t>TC-JFH</t>
+  </si>
+  <si>
+    <t>TC-JFJ</t>
+  </si>
+  <si>
+    <t>TC-JFK</t>
+  </si>
+  <si>
+    <t>TC-JFL</t>
+  </si>
+  <si>
+    <t>TC-JFM</t>
+  </si>
+  <si>
+    <t>TC-JFN</t>
+  </si>
+  <si>
+    <t>TC-JFO</t>
+  </si>
+  <si>
+    <t>TC-JFP</t>
+  </si>
+  <si>
+    <t>TC-JFR</t>
+  </si>
+  <si>
+    <t>TC-JFT</t>
+  </si>
+  <si>
+    <t>TC-JFU</t>
+  </si>
+  <si>
+    <t>TC-JFY</t>
+  </si>
+  <si>
+    <t>TC-JFZ</t>
+  </si>
+  <si>
+    <t>TC-JGC</t>
+  </si>
+  <si>
+    <t>TC-JGE</t>
+  </si>
+  <si>
+    <t>737-8AS</t>
+  </si>
+  <si>
+    <t>TC-JZJ</t>
+  </si>
+  <si>
+    <t>TC-JZV</t>
+  </si>
+  <si>
+    <t>TC-JZL</t>
+  </si>
+  <si>
+    <t>TC-JZK</t>
+  </si>
+  <si>
+    <t>TC-JZU</t>
+  </si>
+  <si>
+    <t>737-8JP</t>
+  </si>
+  <si>
+    <t>TC-JZO</t>
+  </si>
+  <si>
+    <t>TC-JGR</t>
+  </si>
+  <si>
+    <t>TC-JGS</t>
+  </si>
+  <si>
+    <t>TC-JGT</t>
+  </si>
+  <si>
+    <t>TC-JGU</t>
+  </si>
+  <si>
+    <t>TC-JGV</t>
+  </si>
+  <si>
+    <t>TC-JGY</t>
+  </si>
+  <si>
+    <t>TC-JGZ</t>
+  </si>
+  <si>
+    <t>TC-JHA</t>
+  </si>
+  <si>
+    <t>TC-JHB</t>
+  </si>
+  <si>
+    <t>TC-JHC</t>
+  </si>
+  <si>
+    <t>TC-JHD</t>
+  </si>
+  <si>
+    <t>TC-JHE</t>
+  </si>
+  <si>
+    <t>TC-JHF</t>
+  </si>
+  <si>
+    <t>TC-JZN</t>
+  </si>
+  <si>
+    <t>TC-JHK</t>
+  </si>
+  <si>
+    <t>TC-JHL</t>
+  </si>
+  <si>
+    <t>737-86Q</t>
+  </si>
+  <si>
+    <t>TC-JHM</t>
+  </si>
+  <si>
+    <t>TC-JHN</t>
+  </si>
+  <si>
+    <t>TC-JHO</t>
+  </si>
+  <si>
+    <t>TC-JHP</t>
+  </si>
+  <si>
+    <t>TC-JHR</t>
+  </si>
+  <si>
+    <t>TC-JHS</t>
+  </si>
+  <si>
+    <t>TC-JHT</t>
+  </si>
+  <si>
+    <t>TC-JHU</t>
+  </si>
+  <si>
+    <t>TC-JHV</t>
+  </si>
+  <si>
+    <t>TC-JHY</t>
+  </si>
+  <si>
+    <t>TC-JHZ</t>
+  </si>
+  <si>
+    <t>TC-JVA</t>
+  </si>
+  <si>
+    <t>TC-JVB</t>
+  </si>
+  <si>
+    <t>TC-JVC</t>
+  </si>
+  <si>
+    <t>TC-JVD</t>
+  </si>
+  <si>
+    <t>TC-JVE</t>
+  </si>
+  <si>
+    <t>TC-JVF</t>
+  </si>
+  <si>
+    <t>TC-JVG</t>
+  </si>
+  <si>
+    <t>TC-JVH</t>
+  </si>
+  <si>
+    <t>TC-JVI</t>
+  </si>
+  <si>
+    <t>TC-JVJ</t>
+  </si>
+  <si>
+    <t>TC-JVK</t>
+  </si>
+  <si>
+    <t>TC-JVL</t>
+  </si>
+  <si>
+    <t>TC-JVM</t>
+  </si>
+  <si>
+    <t>TC-JVN</t>
+  </si>
+  <si>
+    <t>TC-JVO</t>
+  </si>
+  <si>
+    <t>TC-JVP</t>
+  </si>
+  <si>
+    <t>TC-JVR</t>
+  </si>
+  <si>
+    <t>TC-JVS</t>
+  </si>
+  <si>
+    <t>TC-JVT</t>
+  </si>
+  <si>
+    <t>TC-JVU</t>
+  </si>
+  <si>
+    <t>TC-JVV</t>
+  </si>
+  <si>
+    <t>TC-JVY</t>
+  </si>
+  <si>
+    <t>TC-JVZ</t>
+  </si>
+  <si>
+    <t>TC-JZF</t>
+  </si>
+  <si>
+    <t>TC-JZE</t>
+  </si>
+  <si>
+    <t>TC-JZG</t>
+  </si>
+  <si>
+    <t>TC-JZH</t>
+  </si>
+  <si>
+    <t>737-8Q8</t>
+  </si>
+  <si>
+    <t>TC-JKU</t>
+  </si>
+  <si>
+    <t>TC-JKV</t>
+  </si>
+  <si>
+    <t>TC-JZR</t>
+  </si>
+  <si>
+    <t>TC-JZS</t>
+  </si>
+  <si>
+    <t>TC-JZT</t>
+  </si>
+  <si>
+    <t>737-8KV</t>
+  </si>
+  <si>
+    <t>TC-JZZ</t>
+  </si>
+  <si>
+    <t>737-86N</t>
+  </si>
+  <si>
+    <t>TC-JKY</t>
+  </si>
+  <si>
+    <t>737-752</t>
+  </si>
+  <si>
+    <t>TC-JKO</t>
+  </si>
+  <si>
+    <t>737-73V</t>
+  </si>
+  <si>
+    <t>TC-SAF</t>
+  </si>
+  <si>
+    <t>TC-SAG</t>
+  </si>
+  <si>
+    <t>737-9F2ER</t>
+  </si>
+  <si>
+    <t>TC-JYA</t>
+  </si>
+  <si>
+    <t>TC-JYB</t>
+  </si>
+  <si>
+    <t>TC-JYC</t>
+  </si>
+  <si>
+    <t>TC-JYD</t>
+  </si>
+  <si>
+    <t>TC-JYE</t>
+  </si>
+  <si>
+    <t>TC-JYF</t>
+  </si>
+  <si>
+    <t>TC-JYG</t>
+  </si>
+  <si>
+    <t>TC-JYH</t>
+  </si>
+  <si>
+    <t>TC-JYI</t>
+  </si>
+  <si>
+    <t>TC-JYJ</t>
+  </si>
+  <si>
+    <t>TC-JYL</t>
+  </si>
+  <si>
+    <t>TC-JYM</t>
+  </si>
+  <si>
+    <t>TC-JYN</t>
+  </si>
+  <si>
+    <t>TC-JYO</t>
+  </si>
+  <si>
+    <t>TC-JYP</t>
+  </si>
+  <si>
+    <t>737-8</t>
+  </si>
+  <si>
+    <t>TC-LCA</t>
+  </si>
+  <si>
+    <t>TC-LCF</t>
+  </si>
+  <si>
+    <t>TC-LCD</t>
+  </si>
+  <si>
+    <t>TC-LCB</t>
+  </si>
+  <si>
+    <t>TC-LCC</t>
+  </si>
+  <si>
+    <t>TC-LCE</t>
+  </si>
+  <si>
+    <t>TC-LCG</t>
+  </si>
+  <si>
+    <t>TC-LCK</t>
+  </si>
+  <si>
+    <t>TC-LCJ</t>
+  </si>
+  <si>
+    <t>TC-LCM</t>
+  </si>
+  <si>
+    <t>TC-LCL</t>
+  </si>
+  <si>
+    <t>TC-LCN</t>
+  </si>
+  <si>
+    <t>TC-LCO</t>
+  </si>
+  <si>
+    <t>TC-LCP</t>
+  </si>
+  <si>
+    <t>TC-LCR</t>
+  </si>
+  <si>
+    <t>TC-LCS</t>
+  </si>
+  <si>
+    <t>TC-LCT</t>
+  </si>
+  <si>
+    <t>TC-LCH</t>
+  </si>
+  <si>
+    <t>TC-LCI</t>
+  </si>
+  <si>
+    <t>TC-LCU</t>
+  </si>
+  <si>
+    <t>TC-LAG</t>
+  </si>
+  <si>
+    <t>TC-LAH</t>
+  </si>
+  <si>
+    <t>TC-LAI</t>
+  </si>
+  <si>
+    <t>TC-LAJ</t>
+  </si>
+  <si>
+    <t>TC-LAK</t>
+  </si>
+  <si>
+    <t>TC-LAF</t>
+  </si>
+  <si>
+    <t>TC-LAE</t>
+  </si>
+  <si>
+    <t>TC-OHA</t>
+  </si>
+  <si>
+    <t>TC-OHB</t>
+  </si>
+  <si>
+    <t>TC-OHC</t>
+  </si>
+  <si>
+    <t>TC-OHD</t>
+  </si>
+  <si>
+    <t>TC-OHE</t>
+  </si>
+  <si>
+    <t>TC-OHF</t>
+  </si>
+  <si>
+    <t>TC-VFB</t>
+  </si>
+  <si>
+    <t>TC-OHR</t>
+  </si>
+  <si>
+    <t>TC-OHS</t>
+  </si>
+  <si>
+    <t>TC-OHT</t>
+  </si>
+  <si>
+    <t>TC-OHU</t>
+  </si>
+  <si>
+    <t>TC-OHN</t>
+  </si>
+  <si>
+    <t>TC-OHM</t>
+  </si>
+  <si>
+    <t>TC-OHP</t>
+  </si>
+  <si>
+    <t>TC-VFF</t>
+  </si>
+  <si>
+    <t>TC-VFG</t>
+  </si>
+  <si>
+    <t>TC-OHY</t>
+  </si>
+  <si>
+    <t>TC-OHO</t>
+  </si>
+  <si>
+    <t>TC-OHV</t>
+  </si>
+  <si>
+    <t>TC-OHZ</t>
+  </si>
+  <si>
+    <t>TC-VFC</t>
+  </si>
+  <si>
+    <t>TC-VFA</t>
+  </si>
+  <si>
+    <t>TC-LCV</t>
+  </si>
+  <si>
+    <t>TC-VFI</t>
+  </si>
+  <si>
+    <t>TC-VFK</t>
+  </si>
+  <si>
+    <t>TC-VFH</t>
+  </si>
+  <si>
+    <t>TC-VFD</t>
+  </si>
+  <si>
+    <t>TC-VFL</t>
+  </si>
+  <si>
+    <t>TC-VFJ</t>
+  </si>
+  <si>
+    <t>TC-VFE</t>
+  </si>
+  <si>
+    <t>TC-VFN</t>
+  </si>
+  <si>
+    <t>TC-VFM</t>
+  </si>
+  <si>
+    <t>TC-LCY</t>
+  </si>
+  <si>
+    <t>TC-VFR</t>
+  </si>
+  <si>
+    <t>TC-LDA</t>
+  </si>
+  <si>
+    <t>TC-LCZ</t>
+  </si>
+  <si>
+    <t>TC-VFO</t>
+  </si>
+  <si>
+    <t>TC-LDB</t>
+  </si>
+  <si>
+    <t>TC-VFP</t>
+  </si>
+  <si>
+    <t>TC-LDC</t>
+  </si>
+  <si>
+    <t>737-9</t>
+  </si>
+  <si>
+    <t>TC-LYA</t>
+  </si>
+  <si>
+    <t>TC-LYB</t>
+  </si>
+  <si>
+    <t>TC-LYD</t>
+  </si>
+  <si>
+    <t>TC-LYE</t>
+  </si>
+  <si>
+    <t>TC-LYC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GE90-100 SERIES</t>
+  </si>
+  <si>
+    <t>CFM56 ENGINES (CFM56-7) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEAP-1B ENGINES </t>
+  </si>
+  <si>
+    <t>TC-LRJ</t>
+  </si>
+  <si>
+    <t>TC-LRL</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1156,6 +1888,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1437,15 +2172,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E536"/>
+  <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.1796875" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="32.453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="38.25" customHeight="1" thickBot="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1453,16 +2190,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1479,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1">
+    <row r="3" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1496,7 +2233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1">
+    <row r="4" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1513,7 +2250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1">
+    <row r="5" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1530,7 +2267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1">
+    <row r="6" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1547,7 +2284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1">
+    <row r="7" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1564,7 +2301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1">
+    <row r="8" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1581,7 +2318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1">
+    <row r="9" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1598,7 +2335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1">
+    <row r="10" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1615,7 +2352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1">
+    <row r="11" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1632,7 +2369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1">
+    <row r="12" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1649,7 +2386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1">
+    <row r="13" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1666,7 +2403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1">
+    <row r="14" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1683,7 +2420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1">
+    <row r="15" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1700,7 +2437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1">
+    <row r="16" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1717,7 +2454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1">
+    <row r="17" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -1734,7 +2471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1">
+    <row r="18" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -1751,7 +2488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1">
+    <row r="19" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -1768,7 +2505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1">
+    <row r="20" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1785,7 +2522,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1">
+    <row r="21" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -1802,7 +2539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1">
+    <row r="22" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
@@ -1819,7 +2556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1">
+    <row r="23" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
@@ -1836,7 +2573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1">
+    <row r="24" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
@@ -1853,7 +2590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1">
+    <row r="25" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
@@ -1870,7 +2607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1">
+    <row r="26" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="s">
         <v>34</v>
       </c>
@@ -1887,7 +2624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1">
+    <row r="27" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
@@ -1904,7 +2641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1">
+    <row r="28" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
@@ -1921,7 +2658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1">
+    <row r="29" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
@@ -1938,7 +2675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1">
+    <row r="30" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -1955,7 +2692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1">
+    <row r="31" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A31" s="2" t="s">
         <v>41</v>
       </c>
@@ -1972,7 +2709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1">
+    <row r="32" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A32" s="2" t="s">
         <v>42</v>
       </c>
@@ -1989,7 +2726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1">
+    <row r="33" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A33" s="2" t="s">
         <v>43</v>
       </c>
@@ -2006,7 +2743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1">
+    <row r="34" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
@@ -2023,7 +2760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1">
+    <row r="35" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="2" t="s">
         <v>45</v>
       </c>
@@ -2040,7 +2777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1">
+    <row r="36" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A36" s="2" t="s">
         <v>46</v>
       </c>
@@ -2057,7 +2794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1">
+    <row r="37" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>47</v>
       </c>
@@ -2074,7 +2811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1">
+    <row r="38" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A38" s="2" t="s">
         <v>48</v>
       </c>
@@ -2091,7 +2828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1">
+    <row r="39" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A39" s="2" t="s">
         <v>49</v>
       </c>
@@ -2108,7 +2845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1">
+    <row r="40" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A40" s="2" t="s">
         <v>50</v>
       </c>
@@ -2125,7 +2862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1">
+    <row r="41" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A41" s="2" t="s">
         <v>51</v>
       </c>
@@ -2142,7 +2879,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1">
+    <row r="42" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
@@ -2159,7 +2896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1">
+    <row r="43" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A43" s="2" t="s">
         <v>53</v>
       </c>
@@ -2176,7 +2913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1">
+    <row r="44" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A44" s="2" t="s">
         <v>54</v>
       </c>
@@ -2193,7 +2930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1">
+    <row r="45" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A45" s="2" t="s">
         <v>56</v>
       </c>
@@ -2210,7 +2947,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1">
+    <row r="46" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A46" s="2" t="s">
         <v>58</v>
       </c>
@@ -2227,7 +2964,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" thickBot="1">
+    <row r="47" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A47" s="2" t="s">
         <v>59</v>
       </c>
@@ -2244,7 +2981,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15" thickBot="1">
+    <row r="48" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A48" s="2" t="s">
         <v>60</v>
       </c>
@@ -2261,7 +2998,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1">
+    <row r="49" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -2278,7 +3015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1">
+    <row r="50" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A50" s="2" t="s">
         <v>62</v>
       </c>
@@ -2295,7 +3032,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15" thickBot="1">
+    <row r="51" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A51" s="2" t="s">
         <v>63</v>
       </c>
@@ -2312,7 +3049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1">
+    <row r="52" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A52" s="2" t="s">
         <v>64</v>
       </c>
@@ -2329,7 +3066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1">
+    <row r="53" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
@@ -2346,7 +3083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1">
+    <row r="54" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A54" s="2" t="s">
         <v>66</v>
       </c>
@@ -2363,7 +3100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15" thickBot="1">
+    <row r="55" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A55" s="2" t="s">
         <v>67</v>
       </c>
@@ -2380,7 +3117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15" thickBot="1">
+    <row r="56" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A56" s="2" t="s">
         <v>68</v>
       </c>
@@ -2397,7 +3134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15" thickBot="1">
+    <row r="57" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A57" s="2" t="s">
         <v>69</v>
       </c>
@@ -2414,7 +3151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15" thickBot="1">
+    <row r="58" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A58" s="2" t="s">
         <v>70</v>
       </c>
@@ -2431,7 +3168,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15" thickBot="1">
+    <row r="59" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A59" s="2" t="s">
         <v>71</v>
       </c>
@@ -2448,7 +3185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15" thickBot="1">
+    <row r="60" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A60" s="2" t="s">
         <v>73</v>
       </c>
@@ -2465,7 +3202,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1">
+    <row r="61" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A61" s="2" t="s">
         <v>75</v>
       </c>
@@ -2482,7 +3219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1">
+    <row r="62" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A62" s="2" t="s">
         <v>77</v>
       </c>
@@ -2499,7 +3236,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1">
+    <row r="63" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A63" s="2" t="s">
         <v>80</v>
       </c>
@@ -2516,7 +3253,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1">
+    <row r="64" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A64" s="2" t="s">
         <v>82</v>
       </c>
@@ -2533,7 +3270,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1">
+    <row r="65" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A65" s="2" t="s">
         <v>83</v>
       </c>
@@ -2550,7 +3287,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1">
+    <row r="66" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A66" s="2" t="s">
         <v>84</v>
       </c>
@@ -2567,7 +3304,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1">
+    <row r="67" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A67" s="2" t="s">
         <v>85</v>
       </c>
@@ -2584,7 +3321,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1">
+    <row r="68" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A68" s="2" t="s">
         <v>86</v>
       </c>
@@ -2601,7 +3338,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1">
+    <row r="69" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A69" s="2" t="s">
         <v>87</v>
       </c>
@@ -2618,7 +3355,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1">
+    <row r="70" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A70" s="2" t="s">
         <v>88</v>
       </c>
@@ -2635,7 +3372,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1">
+    <row r="71" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A71" s="2" t="s">
         <v>89</v>
       </c>
@@ -2652,7 +3389,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1">
+    <row r="72" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A72" s="2" t="s">
         <v>90</v>
       </c>
@@ -2669,7 +3406,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1">
+    <row r="73" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A73" s="2" t="s">
         <v>91</v>
       </c>
@@ -2686,7 +3423,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1">
+    <row r="74" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A74" s="2" t="s">
         <v>92</v>
       </c>
@@ -2703,7 +3440,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1">
+    <row r="75" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A75" s="2" t="s">
         <v>93</v>
       </c>
@@ -2720,7 +3457,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1">
+    <row r="76" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A76" s="2" t="s">
         <v>94</v>
       </c>
@@ -2737,7 +3474,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1">
+    <row r="77" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A77" s="2" t="s">
         <v>95</v>
       </c>
@@ -2754,7 +3491,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1">
+    <row r="78" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A78" s="2" t="s">
         <v>96</v>
       </c>
@@ -2771,7 +3508,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1">
+    <row r="79" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A79" s="2" t="s">
         <v>97</v>
       </c>
@@ -2788,7 +3525,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1">
+    <row r="80" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A80" s="2" t="s">
         <v>98</v>
       </c>
@@ -2805,7 +3542,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1">
+    <row r="81" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A81" s="2" t="s">
         <v>100</v>
       </c>
@@ -2822,7 +3559,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1">
+    <row r="82" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A82" s="2" t="s">
         <v>102</v>
       </c>
@@ -2839,7 +3576,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1">
+    <row r="83" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A83" s="2" t="s">
         <v>103</v>
       </c>
@@ -2856,7 +3593,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" thickBot="1">
+    <row r="84" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A84" s="2" t="s">
         <v>104</v>
       </c>
@@ -2873,7 +3610,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1">
+    <row r="85" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A85" s="2" t="s">
         <v>105</v>
       </c>
@@ -2890,7 +3627,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1">
+    <row r="86" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A86" s="2" t="s">
         <v>106</v>
       </c>
@@ -2907,7 +3644,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1">
+    <row r="87" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A87" s="2" t="s">
         <v>108</v>
       </c>
@@ -2924,7 +3661,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1">
+    <row r="88" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A88" s="2" t="s">
         <v>110</v>
       </c>
@@ -2941,7 +3678,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1">
+    <row r="89" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A89" s="2" t="s">
         <v>111</v>
       </c>
@@ -2958,7 +3695,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1">
+    <row r="90" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A90" s="2" t="s">
         <v>112</v>
       </c>
@@ -2975,7 +3712,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1">
+    <row r="91" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A91" s="2" t="s">
         <v>113</v>
       </c>
@@ -2992,7 +3729,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15" thickBot="1">
+    <row r="92" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A92" s="2" t="s">
         <v>114</v>
       </c>
@@ -3009,7 +3746,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15" thickBot="1">
+    <row r="93" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A93" s="2" t="s">
         <v>115</v>
       </c>
@@ -3026,7 +3763,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15" thickBot="1">
+    <row r="94" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A94" s="2" t="s">
         <v>116</v>
       </c>
@@ -3043,7 +3780,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="15" thickBot="1">
+    <row r="95" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A95" s="2" t="s">
         <v>117</v>
       </c>
@@ -3060,7 +3797,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15" thickBot="1">
+    <row r="96" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A96" s="2" t="s">
         <v>118</v>
       </c>
@@ -3077,7 +3814,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15" thickBot="1">
+    <row r="97" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A97" s="2" t="s">
         <v>119</v>
       </c>
@@ -3094,7 +3831,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" thickBot="1">
+    <row r="98" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A98" s="2" t="s">
         <v>120</v>
       </c>
@@ -3111,7 +3848,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15" thickBot="1">
+    <row r="99" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A99" s="2" t="s">
         <v>121</v>
       </c>
@@ -3128,7 +3865,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1">
+    <row r="100" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A100" s="2" t="s">
         <v>122</v>
       </c>
@@ -3145,7 +3882,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1">
+    <row r="101" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A101" s="2" t="s">
         <v>123</v>
       </c>
@@ -3162,7 +3899,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1">
+    <row r="102" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A102" s="2" t="s">
         <v>124</v>
       </c>
@@ -3179,7 +3916,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1">
+    <row r="103" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A103" s="2" t="s">
         <v>125</v>
       </c>
@@ -3196,7 +3933,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1">
+    <row r="104" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A104" s="2" t="s">
         <v>126</v>
       </c>
@@ -3213,7 +3950,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1">
+    <row r="105" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A105" s="2" t="s">
         <v>127</v>
       </c>
@@ -3230,7 +3967,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1">
+    <row r="106" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A106" s="2" t="s">
         <v>128</v>
       </c>
@@ -3247,7 +3984,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1">
+    <row r="107" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A107" s="2" t="s">
         <v>129</v>
       </c>
@@ -3264,7 +4001,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1">
+    <row r="108" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A108" s="2" t="s">
         <v>130</v>
       </c>
@@ -3281,7 +4018,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" thickBot="1">
+    <row r="109" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A109" s="2" t="s">
         <v>131</v>
       </c>
@@ -3298,7 +4035,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1">
+    <row r="110" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A110" s="2" t="s">
         <v>132</v>
       </c>
@@ -3315,7 +4052,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" thickBot="1">
+    <row r="111" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A111" s="2" t="s">
         <v>133</v>
       </c>
@@ -3332,7 +4069,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1">
+    <row r="112" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A112" s="4" t="s">
         <v>134</v>
       </c>
@@ -3349,7 +4086,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" thickBot="1">
+    <row r="113" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A113" s="4" t="s">
         <v>135</v>
       </c>
@@ -3366,7 +4103,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" thickBot="1">
+    <row r="114" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A114" s="4" t="s">
         <v>136</v>
       </c>
@@ -3383,7 +4120,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" thickBot="1">
+    <row r="115" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A115" s="4" t="s">
         <v>137</v>
       </c>
@@ -3400,7 +4137,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" thickBot="1">
+    <row r="116" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A116" s="2" t="s">
         <v>138</v>
       </c>
@@ -3417,7 +4154,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" thickBot="1">
+    <row r="117" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A117" s="2" t="s">
         <v>139</v>
       </c>
@@ -3434,7 +4171,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" thickBot="1">
+    <row r="118" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A118" s="2" t="s">
         <v>140</v>
       </c>
@@ -3451,7 +4188,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" thickBot="1">
+    <row r="119" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A119" s="2" t="s">
         <v>141</v>
       </c>
@@ -3468,7 +4205,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" thickBot="1">
+    <row r="120" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A120" s="2" t="s">
         <v>142</v>
       </c>
@@ -3485,7 +4222,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" thickBot="1">
+    <row r="121" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A121" s="2" t="s">
         <v>143</v>
       </c>
@@ -3502,7 +4239,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" thickBot="1">
+    <row r="122" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A122" s="2" t="s">
         <v>144</v>
       </c>
@@ -3519,7 +4256,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" thickBot="1">
+    <row r="123" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A123" s="2" t="s">
         <v>146</v>
       </c>
@@ -3536,7 +4273,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" thickBot="1">
+    <row r="124" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A124" s="2" t="s">
         <v>148</v>
       </c>
@@ -3553,7 +4290,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" thickBot="1">
+    <row r="125" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A125" s="2" t="s">
         <v>149</v>
       </c>
@@ -3570,7 +4307,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" thickBot="1">
+    <row r="126" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A126" s="2" t="s">
         <v>150</v>
       </c>
@@ -3587,7 +4324,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" thickBot="1">
+    <row r="127" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A127" s="2" t="s">
         <v>151</v>
       </c>
@@ -3604,7 +4341,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" thickBot="1">
+    <row r="128" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A128" s="2" t="s">
         <v>152</v>
       </c>
@@ -3621,7 +4358,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" thickBot="1">
+    <row r="129" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A129" s="2" t="s">
         <v>153</v>
       </c>
@@ -3638,7 +4375,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" thickBot="1">
+    <row r="130" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A130" s="2" t="s">
         <v>154</v>
       </c>
@@ -3655,7 +4392,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" thickBot="1">
+    <row r="131" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A131" s="2" t="s">
         <v>155</v>
       </c>
@@ -3672,7 +4409,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" thickBot="1">
+    <row r="132" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A132" s="2" t="s">
         <v>156</v>
       </c>
@@ -3689,7 +4426,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" thickBot="1">
+    <row r="133" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A133" s="2" t="s">
         <v>157</v>
       </c>
@@ -3706,7 +4443,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" thickBot="1">
+    <row r="134" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A134" s="2" t="s">
         <v>158</v>
       </c>
@@ -3723,7 +4460,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" thickBot="1">
+    <row r="135" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A135" s="2" t="s">
         <v>159</v>
       </c>
@@ -3740,7 +4477,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" thickBot="1">
+    <row r="136" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A136" s="2" t="s">
         <v>160</v>
       </c>
@@ -3757,7 +4494,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" thickBot="1">
+    <row r="137" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A137" s="2" t="s">
         <v>161</v>
       </c>
@@ -3774,7 +4511,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" thickBot="1">
+    <row r="138" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A138" s="2" t="s">
         <v>162</v>
       </c>
@@ -3791,7 +4528,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" thickBot="1">
+    <row r="139" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A139" s="2" t="s">
         <v>163</v>
       </c>
@@ -3808,7 +4545,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" thickBot="1">
+    <row r="140" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A140" s="2" t="s">
         <v>164</v>
       </c>
@@ -3825,7 +4562,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" thickBot="1">
+    <row r="141" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A141" s="2" t="s">
         <v>165</v>
       </c>
@@ -3842,7 +4579,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" thickBot="1">
+    <row r="142" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A142" s="2" t="s">
         <v>166</v>
       </c>
@@ -3859,7 +4596,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" thickBot="1">
+    <row r="143" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A143" s="2" t="s">
         <v>167</v>
       </c>
@@ -3876,7 +4613,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="15" thickBot="1">
+    <row r="144" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A144" s="2" t="s">
         <v>168</v>
       </c>
@@ -3893,7 +4630,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="15" thickBot="1">
+    <row r="145" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A145" s="2" t="s">
         <v>169</v>
       </c>
@@ -3910,7 +4647,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="15" thickBot="1">
+    <row r="146" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A146" s="2" t="s">
         <v>170</v>
       </c>
@@ -3927,7 +4664,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15" thickBot="1">
+    <row r="147" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A147" s="2" t="s">
         <v>171</v>
       </c>
@@ -3944,7 +4681,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="15" thickBot="1">
+    <row r="148" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A148" s="2" t="s">
         <v>172</v>
       </c>
@@ -3961,7 +4698,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="15" thickBot="1">
+    <row r="149" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A149" s="2" t="s">
         <v>173</v>
       </c>
@@ -3978,7 +4715,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="15" thickBot="1">
+    <row r="150" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A150" s="2" t="s">
         <v>174</v>
       </c>
@@ -3995,7 +4732,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="15" thickBot="1">
+    <row r="151" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A151" s="2" t="s">
         <v>175</v>
       </c>
@@ -4012,7 +4749,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="15" thickBot="1">
+    <row r="152" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A152" s="2" t="s">
         <v>176</v>
       </c>
@@ -4029,7 +4766,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="15" thickBot="1">
+    <row r="153" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A153" s="2" t="s">
         <v>177</v>
       </c>
@@ -4046,7 +4783,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="15" thickBot="1">
+    <row r="154" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A154" s="2" t="s">
         <v>178</v>
       </c>
@@ -4063,7 +4800,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="15" thickBot="1">
+    <row r="155" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A155" s="2" t="s">
         <v>179</v>
       </c>
@@ -4080,7 +4817,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15" thickBot="1">
+    <row r="156" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A156" s="2" t="s">
         <v>180</v>
       </c>
@@ -4097,7 +4834,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="15" thickBot="1">
+    <row r="157" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A157" s="2" t="s">
         <v>181</v>
       </c>
@@ -4114,7 +4851,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="15" thickBot="1">
+    <row r="158" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A158" s="2" t="s">
         <v>182</v>
       </c>
@@ -4131,7 +4868,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="15" thickBot="1">
+    <row r="159" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A159" s="2" t="s">
         <v>183</v>
       </c>
@@ -4148,7 +4885,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" thickBot="1">
+    <row r="160" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A160" s="2" t="s">
         <v>184</v>
       </c>
@@ -4165,7 +4902,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="15" thickBot="1">
+    <row r="161" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A161" s="2" t="s">
         <v>185</v>
       </c>
@@ -4182,7 +4919,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1">
+    <row r="162" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A162" s="2" t="s">
         <v>186</v>
       </c>
@@ -4199,7 +4936,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1">
+    <row r="163" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A163" s="2" t="s">
         <v>187</v>
       </c>
@@ -4216,7 +4953,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1">
+    <row r="164" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A164" s="2" t="s">
         <v>188</v>
       </c>
@@ -4233,7 +4970,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1">
+    <row r="165" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A165" s="2" t="s">
         <v>189</v>
       </c>
@@ -4250,7 +4987,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" thickBot="1">
+    <row r="166" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A166" s="2" t="s">
         <v>190</v>
       </c>
@@ -4267,7 +5004,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" thickBot="1">
+    <row r="167" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A167" s="2" t="s">
         <v>191</v>
       </c>
@@ -4284,7 +5021,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" thickBot="1">
+    <row r="168" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A168" s="2" t="s">
         <v>192</v>
       </c>
@@ -4301,7 +5038,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="15" thickBot="1">
+    <row r="169" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A169" s="2" t="s">
         <v>193</v>
       </c>
@@ -4318,7 +5055,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="15" thickBot="1">
+    <row r="170" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A170" s="2" t="s">
         <v>194</v>
       </c>
@@ -4335,7 +5072,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="15" thickBot="1">
+    <row r="171" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A171" s="2" t="s">
         <v>195</v>
       </c>
@@ -4352,7 +5089,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="15" thickBot="1">
+    <row r="172" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A172" s="2" t="s">
         <v>196</v>
       </c>
@@ -4369,7 +5106,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15" thickBot="1">
+    <row r="173" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A173" s="2" t="s">
         <v>197</v>
       </c>
@@ -4386,7 +5123,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="15" thickBot="1">
+    <row r="174" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A174" s="2" t="s">
         <v>198</v>
       </c>
@@ -4403,7 +5140,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="15" thickBot="1">
+    <row r="175" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A175" s="2" t="s">
         <v>199</v>
       </c>
@@ -4420,7 +5157,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="15" thickBot="1">
+    <row r="176" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A176" s="2" t="s">
         <v>200</v>
       </c>
@@ -4437,7 +5174,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="15" thickBot="1">
+    <row r="177" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A177" s="2" t="s">
         <v>201</v>
       </c>
@@ -4454,7 +5191,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="15" thickBot="1">
+    <row r="178" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A178" s="2" t="s">
         <v>202</v>
       </c>
@@ -4471,7 +5208,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="15" thickBot="1">
+    <row r="179" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A179" s="2" t="s">
         <v>203</v>
       </c>
@@ -4488,7 +5225,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15" thickBot="1">
+    <row r="180" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A180" s="2" t="s">
         <v>204</v>
       </c>
@@ -4505,7 +5242,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="15" thickBot="1">
+    <row r="181" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A181" s="2" t="s">
         <v>205</v>
       </c>
@@ -4522,7 +5259,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15" thickBot="1">
+    <row r="182" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A182" s="2" t="s">
         <v>206</v>
       </c>
@@ -4539,7 +5276,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="15" thickBot="1">
+    <row r="183" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A183" s="2" t="s">
         <v>207</v>
       </c>
@@ -4556,7 +5293,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="15" thickBot="1">
+    <row r="184" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A184" s="2" t="s">
         <v>208</v>
       </c>
@@ -4573,7 +5310,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="15" thickBot="1">
+    <row r="185" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A185" s="2" t="s">
         <v>209</v>
       </c>
@@ -4590,7 +5327,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="15" thickBot="1">
+    <row r="186" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A186" s="2" t="s">
         <v>210</v>
       </c>
@@ -4607,7 +5344,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="15" thickBot="1">
+    <row r="187" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A187" s="2" t="s">
         <v>211</v>
       </c>
@@ -4624,7 +5361,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="15" thickBot="1">
+    <row r="188" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A188" s="2" t="s">
         <v>212</v>
       </c>
@@ -4641,7 +5378,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="15" thickBot="1">
+    <row r="189" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A189" s="2" t="s">
         <v>213</v>
       </c>
@@ -4658,7 +5395,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="15" thickBot="1">
+    <row r="190" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A190" s="2" t="s">
         <v>214</v>
       </c>
@@ -4675,7 +5412,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="15" thickBot="1">
+    <row r="191" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A191" s="2" t="s">
         <v>216</v>
       </c>
@@ -4692,7 +5429,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="15" thickBot="1">
+    <row r="192" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A192" s="2" t="s">
         <v>218</v>
       </c>
@@ -4709,7 +5446,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="15" thickBot="1">
+    <row r="193" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A193" s="2" t="s">
         <v>219</v>
       </c>
@@ -4726,7 +5463,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="15" thickBot="1">
+    <row r="194" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A194" s="2" t="s">
         <v>220</v>
       </c>
@@ -4743,7 +5480,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="15" thickBot="1">
+    <row r="195" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A195" s="2" t="s">
         <v>221</v>
       </c>
@@ -4760,7 +5497,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="15" thickBot="1">
+    <row r="196" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A196" s="2" t="s">
         <v>222</v>
       </c>
@@ -4777,7 +5514,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="15" thickBot="1">
+    <row r="197" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A197" s="2" t="s">
         <v>223</v>
       </c>
@@ -4794,7 +5531,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="15" thickBot="1">
+    <row r="198" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A198" s="2" t="s">
         <v>224</v>
       </c>
@@ -4811,7 +5548,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="15" thickBot="1">
+    <row r="199" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A199" s="2" t="s">
         <v>225</v>
       </c>
@@ -4828,7 +5565,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="15" thickBot="1">
+    <row r="200" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A200" s="2" t="s">
         <v>226</v>
       </c>
@@ -4845,7 +5582,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="15" thickBot="1">
+    <row r="201" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A201" s="2" t="s">
         <v>227</v>
       </c>
@@ -4862,7 +5599,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="15" thickBot="1">
+    <row r="202" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A202" s="2" t="s">
         <v>228</v>
       </c>
@@ -4879,7 +5616,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="15" thickBot="1">
+    <row r="203" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A203" s="2" t="s">
         <v>229</v>
       </c>
@@ -4896,7 +5633,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15" thickBot="1">
+    <row r="204" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A204" s="2" t="s">
         <v>230</v>
       </c>
@@ -4913,7 +5650,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="15" thickBot="1">
+    <row r="205" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A205" s="2" t="s">
         <v>231</v>
       </c>
@@ -4930,7 +5667,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="15" thickBot="1">
+    <row r="206" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A206" s="2" t="s">
         <v>232</v>
       </c>
@@ -4947,7 +5684,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="15" thickBot="1">
+    <row r="207" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A207" s="2" t="s">
         <v>233</v>
       </c>
@@ -4964,7 +5701,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="15" thickBot="1">
+    <row r="208" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A208" s="2" t="s">
         <v>234</v>
       </c>
@@ -4981,7 +5718,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="15" thickBot="1">
+    <row r="209" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A209" s="2" t="s">
         <v>235</v>
       </c>
@@ -4998,7 +5735,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="15" thickBot="1">
+    <row r="210" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A210" s="2" t="s">
         <v>236</v>
       </c>
@@ -5015,7 +5752,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="15" thickBot="1">
+    <row r="211" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A211" s="2" t="s">
         <v>237</v>
       </c>
@@ -5032,7 +5769,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="15" thickBot="1">
+    <row r="212" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A212" s="2" t="s">
         <v>238</v>
       </c>
@@ -5049,7 +5786,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="15" thickBot="1">
+    <row r="213" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A213" s="2" t="s">
         <v>239</v>
       </c>
@@ -5066,7 +5803,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="15" thickBot="1">
+    <row r="214" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A214" s="2" t="s">
         <v>240</v>
       </c>
@@ -5083,7 +5820,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="15" thickBot="1">
+    <row r="215" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A215" s="2" t="s">
         <v>241</v>
       </c>
@@ -5100,7 +5837,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="15" thickBot="1">
+    <row r="216" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -5117,7 +5854,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="15" thickBot="1">
+    <row r="217" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A217" s="2" t="s">
         <v>243</v>
       </c>
@@ -5134,7 +5871,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="15" thickBot="1">
+    <row r="218" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A218" s="2" t="s">
         <v>244</v>
       </c>
@@ -5151,7 +5888,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="15" thickBot="1">
+    <row r="219" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A219" s="2" t="s">
         <v>245</v>
       </c>
@@ -5168,7 +5905,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="15" thickBot="1">
+    <row r="220" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A220" s="2" t="s">
         <v>246</v>
       </c>
@@ -5185,7 +5922,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="15" thickBot="1">
+    <row r="221" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A221" s="2" t="s">
         <v>247</v>
       </c>
@@ -5202,7 +5939,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="15" thickBot="1">
+    <row r="222" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A222" s="2" t="s">
         <v>248</v>
       </c>
@@ -5219,7 +5956,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="15" thickBot="1">
+    <row r="223" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A223" s="2" t="s">
         <v>249</v>
       </c>
@@ -5236,7 +5973,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="15" thickBot="1">
+    <row r="224" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A224" s="2" t="s">
         <v>250</v>
       </c>
@@ -5253,7 +5990,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="15" thickBot="1">
+    <row r="225" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A225" s="2" t="s">
         <v>251</v>
       </c>
@@ -5270,7 +6007,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="15" thickBot="1">
+    <row r="226" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A226" s="2" t="s">
         <v>252</v>
       </c>
@@ -5287,7 +6024,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="15" thickBot="1">
+    <row r="227" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A227" s="2" t="s">
         <v>253</v>
       </c>
@@ -5304,7 +6041,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="15" thickBot="1">
+    <row r="228" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A228" s="2" t="s">
         <v>254</v>
       </c>
@@ -5321,7 +6058,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="15" thickBot="1">
+    <row r="229" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A229" s="2" t="s">
         <v>255</v>
       </c>
@@ -5338,7 +6075,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="15" thickBot="1">
+    <row r="230" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A230" s="2" t="s">
         <v>256</v>
       </c>
@@ -5355,7 +6092,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="15" thickBot="1">
+    <row r="231" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A231" s="2" t="s">
         <v>257</v>
       </c>
@@ -5372,7 +6109,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="15" thickBot="1">
+    <row r="232" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A232" s="2" t="s">
         <v>258</v>
       </c>
@@ -5389,7 +6126,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="15" thickBot="1">
+    <row r="233" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A233" s="2" t="s">
         <v>259</v>
       </c>
@@ -5406,7 +6143,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="15" thickBot="1">
+    <row r="234" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A234" s="2" t="s">
         <v>260</v>
       </c>
@@ -5423,7 +6160,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="15" thickBot="1">
+    <row r="235" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A235" s="2" t="s">
         <v>261</v>
       </c>
@@ -5440,7 +6177,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15" thickBot="1">
+    <row r="236" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A236" s="2" t="s">
         <v>262</v>
       </c>
@@ -5457,7 +6194,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="15" thickBot="1">
+    <row r="237" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A237" s="2" t="s">
         <v>263</v>
       </c>
@@ -5474,7 +6211,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="15" thickBot="1">
+    <row r="238" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A238" s="2" t="s">
         <v>264</v>
       </c>
@@ -5491,7 +6228,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="15" thickBot="1">
+    <row r="239" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A239" s="2" t="s">
         <v>265</v>
       </c>
@@ -5508,7 +6245,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="15" thickBot="1">
+    <row r="240" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A240" s="2" t="s">
         <v>266</v>
       </c>
@@ -5525,7 +6262,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="15" thickBot="1">
+    <row r="241" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A241" s="2" t="s">
         <v>267</v>
       </c>
@@ -5542,7 +6279,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="15" thickBot="1">
+    <row r="242" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A242" s="2" t="s">
         <v>268</v>
       </c>
@@ -5559,7 +6296,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="15" thickBot="1">
+    <row r="243" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A243" s="2" t="s">
         <v>269</v>
       </c>
@@ -5576,7 +6313,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="15" thickBot="1">
+    <row r="244" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A244" s="2" t="s">
         <v>270</v>
       </c>
@@ -5593,7 +6330,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="15" thickBot="1">
+    <row r="245" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A245" s="2" t="s">
         <v>271</v>
       </c>
@@ -5610,7 +6347,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="15" thickBot="1">
+    <row r="246" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A246" s="2" t="s">
         <v>272</v>
       </c>
@@ -5627,7 +6364,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15" thickBot="1">
+    <row r="247" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A247" s="2" t="s">
         <v>273</v>
       </c>
@@ -5644,7 +6381,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="15" thickBot="1">
+    <row r="248" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A248" s="2" t="s">
         <v>274</v>
       </c>
@@ -5661,7 +6398,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="15" thickBot="1">
+    <row r="249" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A249" s="2" t="s">
         <v>275</v>
       </c>
@@ -5678,7 +6415,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="15" thickBot="1">
+    <row r="250" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A250" s="2" t="s">
         <v>276</v>
       </c>
@@ -5695,7 +6432,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="15" thickBot="1">
+    <row r="251" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A251" s="2" t="s">
         <v>277</v>
       </c>
@@ -5712,7 +6449,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15" thickBot="1">
+    <row r="252" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A252" s="2" t="s">
         <v>278</v>
       </c>
@@ -5729,7 +6466,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="15" thickBot="1">
+    <row r="253" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A253" s="2" t="s">
         <v>279</v>
       </c>
@@ -5746,7 +6483,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="15" thickBot="1">
+    <row r="254" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A254" s="2" t="s">
         <v>280</v>
       </c>
@@ -5763,7 +6500,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="15" thickBot="1">
+    <row r="255" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A255" s="2" t="s">
         <v>281</v>
       </c>
@@ -5780,7 +6517,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="15" thickBot="1">
+    <row r="256" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A256" s="2" t="s">
         <v>282</v>
       </c>
@@ -5797,7 +6534,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="15" thickBot="1">
+    <row r="257" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A257" s="2" t="s">
         <v>283</v>
       </c>
@@ -5814,7 +6551,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="15" thickBot="1">
+    <row r="258" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A258" s="2" t="s">
         <v>284</v>
       </c>
@@ -5831,7 +6568,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="15" thickBot="1">
+    <row r="259" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A259" s="2" t="s">
         <v>285</v>
       </c>
@@ -5848,7 +6585,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="15" thickBot="1">
+    <row r="260" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A260" s="2" t="s">
         <v>286</v>
       </c>
@@ -5865,7 +6602,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="15" thickBot="1">
+    <row r="261" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A261" s="2" t="s">
         <v>287</v>
       </c>
@@ -5882,7 +6619,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="15" thickBot="1">
+    <row r="262" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A262" s="2" t="s">
         <v>288</v>
       </c>
@@ -5899,7 +6636,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="15" thickBot="1">
+    <row r="263" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A263" s="4" t="s">
         <v>289</v>
       </c>
@@ -5916,7 +6653,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="15" thickBot="1">
+    <row r="264" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A264" s="4" t="s">
         <v>290</v>
       </c>
@@ -5933,9 +6670,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="15" thickBot="1">
+    <row r="265" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A265" s="4" t="s">
-        <v>291</v>
+        <v>583</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>215</v>
@@ -5950,9 +6687,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="15" thickBot="1">
+    <row r="266" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A266" s="4" t="s">
-        <v>292</v>
+        <v>584</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>215</v>
@@ -5967,9 +6704,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="15" thickBot="1">
+    <row r="267" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A267" s="4" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>215</v>
@@ -5984,12 +6721,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="15" thickBot="1">
+    <row r="268" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A268" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C268" s="2">
         <v>801</v>
@@ -5998,15 +6735,15 @@
         <v>4042</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" ht="15" thickBot="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A269" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C269" s="2">
         <v>153</v>
@@ -6015,623 +6752,4550 @@
         <v>902</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" ht="15" thickBot="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A270" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D270" s="2">
         <v>403</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A271" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D271" s="2">
         <v>421</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A272" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D272" s="2">
         <v>435</v>
       </c>
       <c r="E272" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A273" s="2" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" ht="15" thickBot="1">
-      <c r="A273" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="B273" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D273" s="2">
         <v>442</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A274" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D274" s="2">
         <v>454</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A275" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D275" s="2">
         <v>457</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A276" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D276" s="2">
         <v>463</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A277" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D277" s="2">
         <v>471</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A278" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D278" s="2">
         <v>493</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A279" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D279" s="2">
         <v>496</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A280" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D280" s="2">
         <v>565</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A281" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D281" s="2">
         <v>596</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A282" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D282" s="2">
         <v>618</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A283" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D283" s="2">
         <v>621</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A284" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D284" s="2">
         <v>638</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A285" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D285" s="2">
         <v>644</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A286" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D286" s="2">
         <v>651</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A287" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D287" s="2">
         <v>659</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A288" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D288" s="2">
         <v>667</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A289" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D289" s="2">
         <v>669</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A290" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D290" s="2">
         <v>675</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A291" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D291" s="2">
         <v>678</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A292" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D292" s="2">
         <v>682</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A293" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D293" s="2">
         <v>688</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A294" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D294" s="2">
         <v>716</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A295" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D295" s="2">
         <v>721</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A296" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D296" s="2">
         <v>725</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A297" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D297" s="2">
         <v>727</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A298" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D298" s="2">
         <v>734</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A299" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D299" s="2">
         <v>745</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A300" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D300" s="2">
         <v>753</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A301" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D301" s="2">
         <v>759</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A302" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D302" s="2">
         <v>766</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A303" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D303" s="2">
         <v>777</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A304" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D304" s="2">
         <v>793</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" ht="15" thickBot="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A305" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C305" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="D305" s="2">
         <v>822</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A306" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C306" s="2">
+        <v>1</v>
+      </c>
+      <c r="D306" s="2">
+        <v>40707</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A307" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C307" s="2">
+        <v>2</v>
+      </c>
+      <c r="D307" s="2">
+        <v>40708</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A308" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C308" s="2">
+        <v>3</v>
+      </c>
+      <c r="D308" s="2">
+        <v>40791</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A309" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C309" s="2">
+        <v>4</v>
+      </c>
+      <c r="D309" s="2">
+        <v>40792</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A310" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C310" s="2">
+        <v>5</v>
+      </c>
+      <c r="D310" s="2">
+        <v>40709</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A311" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C311" s="2">
+        <v>6</v>
+      </c>
+      <c r="D311" s="2">
+        <v>40710</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A312" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C312" s="2">
+        <v>7</v>
+      </c>
+      <c r="D312" s="2">
+        <v>40711</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A313" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C313" s="2">
+        <v>8</v>
+      </c>
+      <c r="D313" s="2">
+        <v>40793</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A314" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C314" s="2">
+        <v>9</v>
+      </c>
+      <c r="D314" s="2">
+        <v>40794</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A315" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C315" s="2">
+        <v>10</v>
+      </c>
+      <c r="D315" s="2">
+        <v>40795</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A316" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C316" s="2">
+        <v>11</v>
+      </c>
+      <c r="D316" s="2">
+        <v>40796</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A317" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C317" s="2">
+        <v>12</v>
+      </c>
+      <c r="D317" s="2">
+        <v>40797</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A318" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C318" s="2">
+        <v>13</v>
+      </c>
+      <c r="D318" s="2">
+        <v>44116</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A319" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C319" s="2">
+        <v>14</v>
+      </c>
+      <c r="D319" s="2">
+        <v>44117</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A320" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C320" s="2">
+        <v>15</v>
+      </c>
+      <c r="D320" s="2">
+        <v>44118</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A321" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C321" s="2">
+        <v>16</v>
+      </c>
+      <c r="D321" s="2">
+        <v>60401</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A322" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C322" s="2">
+        <v>17</v>
+      </c>
+      <c r="D322" s="2">
+        <v>44119</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A323" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C323" s="2">
+        <v>18</v>
+      </c>
+      <c r="D323" s="2">
+        <v>44120</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A324" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C324" s="2">
+        <v>19</v>
+      </c>
+      <c r="D324" s="2">
+        <v>44122</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A325" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C325" s="2">
+        <v>20</v>
+      </c>
+      <c r="D325" s="2">
+        <v>44121</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A326" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C326" s="2">
+        <v>21</v>
+      </c>
+      <c r="D326" s="2">
+        <v>44124</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A327" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C327" s="2">
+        <v>22</v>
+      </c>
+      <c r="D327" s="2">
+        <v>44123</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A328" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C328" s="2">
+        <v>23</v>
+      </c>
+      <c r="D328" s="2">
+        <v>44125</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A329" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C329" s="2">
+        <v>24</v>
+      </c>
+      <c r="D329" s="2">
+        <v>44126</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A330" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C330" s="2">
+        <v>25</v>
+      </c>
+      <c r="D330" s="2">
+        <v>44127</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A331" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C331" s="2">
+        <v>26</v>
+      </c>
+      <c r="D331" s="2">
+        <v>44128</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A332" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C332" s="2">
+        <v>27</v>
+      </c>
+      <c r="D332" s="2">
+        <v>44129</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A333" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C333" s="2">
+        <v>28</v>
+      </c>
+      <c r="D333" s="2">
+        <v>44130</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A334" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C334" s="2">
+        <v>29</v>
+      </c>
+      <c r="D334" s="2">
+        <v>60405</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A335" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C335" s="2">
+        <v>30</v>
+      </c>
+      <c r="D335" s="2">
+        <v>60402</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A336" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C336" s="2">
+        <v>35</v>
+      </c>
+      <c r="D336" s="2">
+        <v>41818</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A337" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C337" s="2">
+        <v>36</v>
+      </c>
+      <c r="D337" s="2">
+        <v>41819</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A338" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C338" s="2">
+        <v>37</v>
+      </c>
+      <c r="D338" s="2">
+        <v>42097</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A339" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C339" s="2">
+        <v>101</v>
+      </c>
+      <c r="D339" s="2">
+        <v>60403</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A340" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C340" s="2">
+        <v>102</v>
+      </c>
+      <c r="D340" s="2">
+        <v>60404</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A341" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C341" s="2">
+        <v>103</v>
+      </c>
+      <c r="D341" s="2">
+        <v>65742</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A342" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C342" s="2">
+        <v>104</v>
+      </c>
+      <c r="D342" s="2">
+        <v>65743</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A343" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C343" s="2">
+        <v>105</v>
+      </c>
+      <c r="D343" s="2">
+        <v>65744</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A344" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C344" s="2">
+        <v>106</v>
+      </c>
+      <c r="D344" s="2">
+        <v>66578</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A345" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C345" s="2">
+        <v>107</v>
+      </c>
+      <c r="D345" s="2">
+        <v>66579</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A346" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C346" s="2">
+        <v>108</v>
+      </c>
+      <c r="D346" s="2">
+        <v>66580</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A347" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C347" s="2">
+        <v>109</v>
+      </c>
+      <c r="D347" s="2">
+        <v>35783</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A348" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C348" s="2">
+        <v>110</v>
+      </c>
+      <c r="D348" s="2">
+        <v>32729</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A349" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C349" s="2">
+        <v>111</v>
+      </c>
+      <c r="D349" s="2">
+        <v>32714</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A350" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C350" s="2">
+        <v>112</v>
+      </c>
+      <c r="D350" s="2">
+        <v>70425</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A351" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C351" s="2">
+        <v>113</v>
+      </c>
+      <c r="D351" s="2">
+        <v>70426</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A352" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C352" s="2">
+        <v>114</v>
+      </c>
+      <c r="D352" s="2">
+        <v>70427</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A353" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C353" s="2">
+        <v>115</v>
+      </c>
+      <c r="D353" s="2">
+        <v>70424</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A354" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C354" s="2">
+        <v>1</v>
+      </c>
+      <c r="D354" s="2">
+        <v>29765</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A355" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C355" s="2">
+        <v>2</v>
+      </c>
+      <c r="D355" s="2">
+        <v>29766</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A356" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C356" s="2">
+        <v>3</v>
+      </c>
+      <c r="D356" s="2">
+        <v>29767</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A357" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C357" s="2">
+        <v>4</v>
+      </c>
+      <c r="D357" s="2">
+        <v>29768</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A358" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C358" s="2">
+        <v>5</v>
+      </c>
+      <c r="D358" s="2">
+        <v>29769</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A359" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C359" s="2">
+        <v>6</v>
+      </c>
+      <c r="D359" s="2">
+        <v>29770</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A360" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C360" s="2">
+        <v>7</v>
+      </c>
+      <c r="D360" s="2">
+        <v>29771</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A361" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C361" s="2">
+        <v>8</v>
+      </c>
+      <c r="D361" s="2">
+        <v>29772</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A362" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C362" s="2">
+        <v>9</v>
+      </c>
+      <c r="D362" s="2">
+        <v>29773</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A363" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C363" s="2">
+        <v>10</v>
+      </c>
+      <c r="D363" s="2">
+        <v>29774</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A364" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C364" s="2">
+        <v>11</v>
+      </c>
+      <c r="D364" s="2">
+        <v>29775</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A365" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C365" s="2">
+        <v>12</v>
+      </c>
+      <c r="D365" s="2">
+        <v>29776</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A366" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C366" s="2">
+        <v>13</v>
+      </c>
+      <c r="D366" s="2">
+        <v>29777</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A367" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C367" s="2">
+        <v>14</v>
+      </c>
+      <c r="D367" s="2">
+        <v>29778</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A368" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C368" s="2">
+        <v>15</v>
+      </c>
+      <c r="D368" s="2">
+        <v>29779</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A369" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C369" s="2">
+        <v>16</v>
+      </c>
+      <c r="D369" s="2">
+        <v>29780</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A370" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C370" s="2">
+        <v>17</v>
+      </c>
+      <c r="D370" s="2">
+        <v>29781</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A371" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C371" s="2">
+        <v>19</v>
+      </c>
+      <c r="D371" s="2">
+        <v>29783</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A372" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C372" s="2">
+        <v>20</v>
+      </c>
+      <c r="D372" s="2">
+        <v>29784</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A373" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C373" s="2">
+        <v>21</v>
+      </c>
+      <c r="D373" s="2">
+        <v>29785</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A374" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C374" s="2">
+        <v>23</v>
+      </c>
+      <c r="D374" s="2">
+        <v>29787</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A375" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C375" s="2">
+        <v>25</v>
+      </c>
+      <c r="D375" s="2">
+        <v>29789</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A376" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C376" s="2">
+        <v>26</v>
+      </c>
+      <c r="D376" s="2">
+        <v>29790</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A377" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C377" s="2">
+        <v>28</v>
+      </c>
+      <c r="D377" s="2">
+        <v>34406</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A378" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C378" s="2">
+        <v>30</v>
+      </c>
+      <c r="D378" s="2">
+        <v>34995</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A379" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C379" s="2">
+        <v>32</v>
+      </c>
+      <c r="D379" s="2">
+        <v>40319</v>
+      </c>
+      <c r="E379" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A380" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C380" s="2">
+        <v>33</v>
+      </c>
+      <c r="D380" s="2">
+        <v>34999</v>
+      </c>
+      <c r="E380" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A381" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C381" s="2">
+        <v>34</v>
+      </c>
+      <c r="D381" s="2">
+        <v>34996</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A382" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C382" s="2">
+        <v>35</v>
+      </c>
+      <c r="D382" s="2">
+        <v>40316</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A383" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C383" s="2">
+        <v>36</v>
+      </c>
+      <c r="D383" s="2">
+        <v>39027</v>
+      </c>
+      <c r="E383" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A384" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C384" s="2">
+        <v>37</v>
+      </c>
+      <c r="D384" s="2">
+        <v>34415</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A385" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C385" s="2">
+        <v>38</v>
+      </c>
+      <c r="D385" s="2">
+        <v>34416</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A386" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C386" s="2">
+        <v>39</v>
+      </c>
+      <c r="D386" s="2">
+        <v>34417</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A387" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C387" s="2">
+        <v>40</v>
+      </c>
+      <c r="D387" s="2">
+        <v>34418</v>
+      </c>
+      <c r="E387" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A388" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C388" s="2">
+        <v>41</v>
+      </c>
+      <c r="D388" s="2">
+        <v>34419</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A389" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C389" s="2">
+        <v>42</v>
+      </c>
+      <c r="D389" s="2">
+        <v>35738</v>
+      </c>
+      <c r="E389" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A390" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C390" s="2">
+        <v>43</v>
+      </c>
+      <c r="D390" s="2">
+        <v>35739</v>
+      </c>
+      <c r="E390" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A391" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C391" s="2">
+        <v>44</v>
+      </c>
+      <c r="D391" s="2">
+        <v>35740</v>
+      </c>
+      <c r="E391" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A392" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C392" s="2">
+        <v>45</v>
+      </c>
+      <c r="D392" s="2">
+        <v>35741</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A393" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C393" s="2">
+        <v>46</v>
+      </c>
+      <c r="D393" s="2">
+        <v>35742</v>
+      </c>
+      <c r="E393" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A394" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C394" s="2">
+        <v>47</v>
+      </c>
+      <c r="D394" s="2">
+        <v>35743</v>
+      </c>
+      <c r="E394" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A395" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C395" s="2">
+        <v>48</v>
+      </c>
+      <c r="D395" s="2">
+        <v>35744</v>
+      </c>
+      <c r="E395" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A396" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C396" s="2">
+        <v>49</v>
+      </c>
+      <c r="D396" s="2">
+        <v>35745</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A397" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C397" s="2">
+        <v>50</v>
+      </c>
+      <c r="D397" s="2">
+        <v>39029</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A398" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C398" s="2">
+        <v>51</v>
+      </c>
+      <c r="D398" s="2">
+        <v>39026</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A399" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C399" s="2">
+        <v>53</v>
+      </c>
+      <c r="D399" s="2">
+        <v>40975</v>
+      </c>
+      <c r="E399" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A400" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C400" s="2">
+        <v>54</v>
+      </c>
+      <c r="D400" s="2">
+        <v>40976</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A401" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C401" s="2">
+        <v>55</v>
+      </c>
+      <c r="D401" s="2">
+        <v>30296</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A402" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C402" s="2">
+        <v>56</v>
+      </c>
+      <c r="D402" s="2">
+        <v>40980</v>
+      </c>
+      <c r="E402" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A403" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C403" s="2">
+        <v>57</v>
+      </c>
+      <c r="D403" s="2">
+        <v>40981</v>
+      </c>
+      <c r="E403" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A404" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C404" s="2">
+        <v>58</v>
+      </c>
+      <c r="D404" s="2">
+        <v>40987</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A405" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C405" s="2">
+        <v>59</v>
+      </c>
+      <c r="D405" s="2">
+        <v>42000</v>
+      </c>
+      <c r="E405" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A406" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C406" s="2">
+        <v>60</v>
+      </c>
+      <c r="D406" s="2">
+        <v>40989</v>
+      </c>
+      <c r="E406" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A407" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C407" s="2">
+        <v>61</v>
+      </c>
+      <c r="D407" s="2">
+        <v>40991</v>
+      </c>
+      <c r="E407" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A408" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C408" s="2">
+        <v>62</v>
+      </c>
+      <c r="D408" s="2">
+        <v>42001</v>
+      </c>
+      <c r="E408" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A409" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C409" s="2">
+        <v>63</v>
+      </c>
+      <c r="D409" s="2">
+        <v>42002</v>
+      </c>
+      <c r="E409" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A410" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C410" s="2">
+        <v>64</v>
+      </c>
+      <c r="D410" s="2">
+        <v>40992</v>
+      </c>
+      <c r="E410" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A411" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C411" s="2">
+        <v>65</v>
+      </c>
+      <c r="D411" s="2">
+        <v>42003</v>
+      </c>
+      <c r="E411" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A412" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C412" s="2">
+        <v>66</v>
+      </c>
+      <c r="D412" s="2">
+        <v>42004</v>
+      </c>
+      <c r="E412" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A413" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C413" s="2">
+        <v>67</v>
+      </c>
+      <c r="D413" s="2">
+        <v>40988</v>
+      </c>
+      <c r="E413" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A414" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C414" s="2">
+        <v>68</v>
+      </c>
+      <c r="D414" s="2">
+        <v>40990</v>
+      </c>
+      <c r="E414" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A415" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C415" s="2">
+        <v>69</v>
+      </c>
+      <c r="D415" s="2">
+        <v>42005</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A416" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C416" s="2">
+        <v>70</v>
+      </c>
+      <c r="D416" s="2">
+        <v>42007</v>
+      </c>
+      <c r="E416" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A417" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C417" s="2">
+        <v>71</v>
+      </c>
+      <c r="D417" s="2">
+        <v>42006</v>
+      </c>
+      <c r="E417" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A418" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C418" s="2">
+        <v>72</v>
+      </c>
+      <c r="D418" s="2">
+        <v>42008</v>
+      </c>
+      <c r="E418" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A419" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C419" s="2">
+        <v>73</v>
+      </c>
+      <c r="D419" s="2">
+        <v>42009</v>
+      </c>
+      <c r="E419" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A420" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C420" s="2">
+        <v>74</v>
+      </c>
+      <c r="D420" s="2">
+        <v>60012</v>
+      </c>
+      <c r="E420" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A421" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C421" s="2">
+        <v>75</v>
+      </c>
+      <c r="D421" s="2">
+        <v>60013</v>
+      </c>
+      <c r="E421" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A422" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C422" s="2">
+        <v>76</v>
+      </c>
+      <c r="D422" s="2">
+        <v>60015</v>
+      </c>
+      <c r="E422" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A423" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C423" s="2">
+        <v>77</v>
+      </c>
+      <c r="D423" s="2">
+        <v>60014</v>
+      </c>
+      <c r="E423" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A424" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C424" s="2">
+        <v>78</v>
+      </c>
+      <c r="D424" s="2">
+        <v>60017</v>
+      </c>
+      <c r="E424" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A425" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C425" s="2">
+        <v>79</v>
+      </c>
+      <c r="D425" s="2">
+        <v>60016</v>
+      </c>
+      <c r="E425" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A426" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C426" s="2">
+        <v>80</v>
+      </c>
+      <c r="D426" s="2">
+        <v>60018</v>
+      </c>
+      <c r="E426" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A427" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C427" s="2">
+        <v>81</v>
+      </c>
+      <c r="D427" s="2">
+        <v>60031</v>
+      </c>
+      <c r="E427" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A428" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C428" s="2">
+        <v>82</v>
+      </c>
+      <c r="D428" s="2">
+        <v>60019</v>
+      </c>
+      <c r="E428" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A429" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C429" s="2">
+        <v>83</v>
+      </c>
+      <c r="D429" s="2">
+        <v>60030</v>
+      </c>
+      <c r="E429" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A430" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C430" s="2">
+        <v>84</v>
+      </c>
+      <c r="D430" s="2">
+        <v>60021</v>
+      </c>
+      <c r="E430" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A431" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C431" s="2">
+        <v>85</v>
+      </c>
+      <c r="D431" s="2">
+        <v>60020</v>
+      </c>
+      <c r="E431" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A432" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C432" s="2">
+        <v>86</v>
+      </c>
+      <c r="D432" s="2">
+        <v>60022</v>
+      </c>
+      <c r="E432" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A433" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C433" s="2">
+        <v>87</v>
+      </c>
+      <c r="D433" s="2">
+        <v>60023</v>
+      </c>
+      <c r="E433" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A434" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C434" s="2">
+        <v>88</v>
+      </c>
+      <c r="D434" s="2">
+        <v>60024</v>
+      </c>
+      <c r="E434" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A435" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C435" s="2">
+        <v>89</v>
+      </c>
+      <c r="D435" s="2">
+        <v>60025</v>
+      </c>
+      <c r="E435" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A436" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C436" s="2">
+        <v>90</v>
+      </c>
+      <c r="D436" s="2">
+        <v>60027</v>
+      </c>
+      <c r="E436" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A437" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C437" s="2">
+        <v>91</v>
+      </c>
+      <c r="D437" s="2">
+        <v>60026</v>
+      </c>
+      <c r="E437" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A438" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C438" s="2">
+        <v>92</v>
+      </c>
+      <c r="D438" s="2">
+        <v>60028</v>
+      </c>
+      <c r="E438" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A439" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C439" s="2">
+        <v>93</v>
+      </c>
+      <c r="D439" s="2">
+        <v>60029</v>
+      </c>
+      <c r="E439" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A440" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C440" s="2">
+        <v>94</v>
+      </c>
+      <c r="D440" s="2">
+        <v>41805</v>
+      </c>
+      <c r="E440" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A441" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C441" s="2">
+        <v>95</v>
+      </c>
+      <c r="D441" s="2">
+        <v>41808</v>
+      </c>
+      <c r="E441" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A442" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C442" s="2">
+        <v>96</v>
+      </c>
+      <c r="D442" s="2">
+        <v>39030</v>
+      </c>
+      <c r="E442" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A443" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C443" s="2">
+        <v>97</v>
+      </c>
+      <c r="D443" s="2">
+        <v>39031</v>
+      </c>
+      <c r="E443" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A444" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C444" s="2">
+        <v>98</v>
+      </c>
+      <c r="D444" s="2">
+        <v>39032</v>
+      </c>
+      <c r="E444" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A445" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C445" s="2">
+        <v>101</v>
+      </c>
+      <c r="D445" s="2">
+        <v>60176</v>
+      </c>
+      <c r="E445" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A446" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C446" s="2">
+        <v>102</v>
+      </c>
+      <c r="D446" s="2">
+        <v>32736</v>
+      </c>
+      <c r="E446" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A447" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C447" s="2">
+        <v>117</v>
+      </c>
+      <c r="D447" s="2">
+        <v>34300</v>
+      </c>
+      <c r="E447" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A448" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C448" s="2">
+        <v>123</v>
+      </c>
+      <c r="D448" s="2">
+        <v>32419</v>
+      </c>
+      <c r="E448" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A449" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C449" s="2">
+        <v>124</v>
+      </c>
+      <c r="D449" s="2">
+        <v>32420</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A450" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C450" s="2">
+        <v>201</v>
+      </c>
+      <c r="D450" s="2">
+        <v>40973</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A451" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C451" s="2">
+        <v>202</v>
+      </c>
+      <c r="D451" s="2">
+        <v>40974</v>
+      </c>
+      <c r="E451" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A452" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C452" s="2">
+        <v>203</v>
+      </c>
+      <c r="D452" s="2">
+        <v>40977</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A453" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C453" s="2">
+        <v>204</v>
+      </c>
+      <c r="D453" s="2">
+        <v>40978</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A454" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C454" s="2">
+        <v>205</v>
+      </c>
+      <c r="D454" s="2">
+        <v>40979</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A455" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C455" s="2">
+        <v>206</v>
+      </c>
+      <c r="D455" s="2">
+        <v>40982</v>
+      </c>
+      <c r="E455" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A456" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C456" s="2">
+        <v>207</v>
+      </c>
+      <c r="D456" s="2">
+        <v>40983</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A457" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C457" s="2">
+        <v>208</v>
+      </c>
+      <c r="D457" s="2">
+        <v>40984</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A458" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C458" s="2">
+        <v>209</v>
+      </c>
+      <c r="D458" s="2">
+        <v>40985</v>
+      </c>
+      <c r="E458" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A459" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C459" s="2">
+        <v>210</v>
+      </c>
+      <c r="D459" s="2">
+        <v>40986</v>
+      </c>
+      <c r="E459" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A460" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C460" s="2">
+        <v>211</v>
+      </c>
+      <c r="D460" s="2">
+        <v>42010</v>
+      </c>
+      <c r="E460" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A461" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C461" s="2">
+        <v>212</v>
+      </c>
+      <c r="D461" s="2">
+        <v>42011</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A462" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C462" s="2">
+        <v>213</v>
+      </c>
+      <c r="D462" s="2">
+        <v>42012</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A463" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C463" s="2">
+        <v>214</v>
+      </c>
+      <c r="D463" s="2">
+        <v>42013</v>
+      </c>
+      <c r="E463" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A464" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C464" s="2">
+        <v>215</v>
+      </c>
+      <c r="D464" s="2">
+        <v>42014</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A465" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C465" s="2">
+        <v>1</v>
+      </c>
+      <c r="D465" s="2">
+        <v>60032</v>
+      </c>
+      <c r="E465" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A466" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C466" s="2">
+        <v>2</v>
+      </c>
+      <c r="D466" s="2">
+        <v>60037</v>
+      </c>
+      <c r="E466" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A467" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C467" s="2">
+        <v>3</v>
+      </c>
+      <c r="D467" s="2">
+        <v>60035</v>
+      </c>
+      <c r="E467" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A468" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C468" s="2">
+        <v>4</v>
+      </c>
+      <c r="D468" s="2">
+        <v>60033</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A469" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C469" s="2">
+        <v>5</v>
+      </c>
+      <c r="D469" s="2">
+        <v>60034</v>
+      </c>
+      <c r="E469" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A470" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C470" s="2">
+        <v>6</v>
+      </c>
+      <c r="D470" s="2">
+        <v>60036</v>
+      </c>
+      <c r="E470" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A471" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C471" s="2">
+        <v>7</v>
+      </c>
+      <c r="D471" s="2">
+        <v>60038</v>
+      </c>
+      <c r="E471" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A472" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C472" s="2">
+        <v>8</v>
+      </c>
+      <c r="D472" s="2">
+        <v>60053</v>
+      </c>
+      <c r="E472" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A473" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C473" s="2">
+        <v>9</v>
+      </c>
+      <c r="D473" s="2">
+        <v>60052</v>
+      </c>
+      <c r="E473" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A474" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C474" s="2">
+        <v>10</v>
+      </c>
+      <c r="D474" s="2">
+        <v>60055</v>
+      </c>
+      <c r="E474" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A475" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C475" s="2">
+        <v>11</v>
+      </c>
+      <c r="D475" s="2">
+        <v>60054</v>
+      </c>
+      <c r="E475" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A476" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C476" s="2">
+        <v>12</v>
+      </c>
+      <c r="D476" s="2">
+        <v>60056</v>
+      </c>
+      <c r="E476" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A477" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C477" s="2">
+        <v>13</v>
+      </c>
+      <c r="D477" s="2">
+        <v>60057</v>
+      </c>
+      <c r="E477" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A478" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C478" s="2">
+        <v>14</v>
+      </c>
+      <c r="D478" s="2">
+        <v>60058</v>
+      </c>
+      <c r="E478" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A479" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C479" s="2">
+        <v>15</v>
+      </c>
+      <c r="D479" s="2">
+        <v>60059</v>
+      </c>
+      <c r="E479" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A480" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C480" s="2">
+        <v>16</v>
+      </c>
+      <c r="D480" s="2">
+        <v>60060</v>
+      </c>
+      <c r="E480" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A481" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C481" s="2">
+        <v>17</v>
+      </c>
+      <c r="D481" s="2">
+        <v>60061</v>
+      </c>
+      <c r="E481" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A482" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C482" s="2">
+        <v>18</v>
+      </c>
+      <c r="D482" s="2">
+        <v>60040</v>
+      </c>
+      <c r="E482" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A483" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C483" s="2">
+        <v>19</v>
+      </c>
+      <c r="D483" s="2">
+        <v>60042</v>
+      </c>
+      <c r="E483" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A484" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C484" s="2">
+        <v>20</v>
+      </c>
+      <c r="D484" s="2">
+        <v>60068</v>
+      </c>
+      <c r="E484" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A485" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C485" s="2">
+        <v>21</v>
+      </c>
+      <c r="D485" s="2">
+        <v>61810</v>
+      </c>
+      <c r="E485" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A486" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C486" s="2">
+        <v>22</v>
+      </c>
+      <c r="D486" s="2">
+        <v>61845</v>
+      </c>
+      <c r="E486" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A487" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C487" s="2">
+        <v>23</v>
+      </c>
+      <c r="D487" s="2">
+        <v>64947</v>
+      </c>
+      <c r="E487" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A488" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C488" s="2">
+        <v>24</v>
+      </c>
+      <c r="D488" s="2">
+        <v>61811</v>
+      </c>
+      <c r="E488" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A489" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C489" s="2">
+        <v>25</v>
+      </c>
+      <c r="D489" s="2">
+        <v>61848</v>
+      </c>
+      <c r="E489" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A490" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C490" s="2">
+        <v>26</v>
+      </c>
+      <c r="D490" s="2">
+        <v>65741</v>
+      </c>
+      <c r="E490" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A491" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C491" s="2">
+        <v>27</v>
+      </c>
+      <c r="D491" s="2">
+        <v>44656</v>
+      </c>
+      <c r="E491" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A492" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C492" s="2">
+        <v>28</v>
+      </c>
+      <c r="D492" s="2">
+        <v>65213</v>
+      </c>
+      <c r="E492" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A493" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C493" s="2">
+        <v>29</v>
+      </c>
+      <c r="D493" s="2">
+        <v>65235</v>
+      </c>
+      <c r="E493" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A494" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C494" s="2">
+        <v>30</v>
+      </c>
+      <c r="D494" s="2">
+        <v>65228</v>
+      </c>
+      <c r="E494" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A495" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C495" s="2">
+        <v>31</v>
+      </c>
+      <c r="D495" s="2">
+        <v>66414</v>
+      </c>
+      <c r="E495" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A496" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C496" s="2">
+        <v>32</v>
+      </c>
+      <c r="D496" s="2">
+        <v>65234</v>
+      </c>
+      <c r="E496" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A497" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C497" s="2">
+        <v>33</v>
+      </c>
+      <c r="D497" s="2">
+        <v>65193</v>
+      </c>
+      <c r="E497" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A498" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C498" s="2">
+        <v>34</v>
+      </c>
+      <c r="D498" s="2">
+        <v>66422</v>
+      </c>
+      <c r="E498" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A499" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C499" s="2">
+        <v>35</v>
+      </c>
+      <c r="D499" s="2">
+        <v>61301</v>
+      </c>
+      <c r="E499" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A500" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C500" s="2">
+        <v>36</v>
+      </c>
+      <c r="D500" s="2">
+        <v>60718</v>
+      </c>
+      <c r="E500" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A501" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C501" s="2">
+        <v>37</v>
+      </c>
+      <c r="D501" s="2">
+        <v>60719</v>
+      </c>
+      <c r="E501" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A502" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C502" s="2">
+        <v>38</v>
+      </c>
+      <c r="D502" s="2">
+        <v>62937</v>
+      </c>
+      <c r="E502" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A503" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C503" s="2">
+        <v>39</v>
+      </c>
+      <c r="D503" s="2">
+        <v>66760</v>
+      </c>
+      <c r="E503" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A504" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C504" s="2">
+        <v>40</v>
+      </c>
+      <c r="D504" s="2">
+        <v>66309</v>
+      </c>
+      <c r="E504" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A505" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C505" s="2">
+        <v>41</v>
+      </c>
+      <c r="D505" s="2">
+        <v>66310</v>
+      </c>
+      <c r="E505" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A506" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C506" s="2">
+        <v>42</v>
+      </c>
+      <c r="D506" s="2">
+        <v>62960</v>
+      </c>
+      <c r="E506" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A507" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C507" s="2">
+        <v>43</v>
+      </c>
+      <c r="D507" s="2">
+        <v>60721</v>
+      </c>
+      <c r="E507" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A508" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C508" s="2">
+        <v>44</v>
+      </c>
+      <c r="D508" s="2">
+        <v>66311</v>
+      </c>
+      <c r="E508" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A509" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C509" s="2">
+        <v>45</v>
+      </c>
+      <c r="D509" s="2">
+        <v>66765</v>
+      </c>
+      <c r="E509" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A510" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C510" s="2">
+        <v>46</v>
+      </c>
+      <c r="D510" s="2">
+        <v>66762</v>
+      </c>
+      <c r="E510" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A511" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C511" s="2">
+        <v>47</v>
+      </c>
+      <c r="D511" s="2">
+        <v>66312</v>
+      </c>
+      <c r="E511" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A512" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C512" s="2">
+        <v>48</v>
+      </c>
+      <c r="D512" s="2">
+        <v>66423</v>
+      </c>
+      <c r="E512" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A513" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C513" s="2">
+        <v>49</v>
+      </c>
+      <c r="D513" s="2">
+        <v>66766</v>
+      </c>
+      <c r="E513" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A514" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C514" s="2">
+        <v>50</v>
+      </c>
+      <c r="D514" s="2">
+        <v>62939</v>
+      </c>
+      <c r="E514" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A515" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C515" s="2">
+        <v>51</v>
+      </c>
+      <c r="D515" s="2">
+        <v>62940</v>
+      </c>
+      <c r="E515" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A516" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C516" s="2">
+        <v>52</v>
+      </c>
+      <c r="D516" s="2">
+        <v>62961</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A517" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C517" s="2">
+        <v>53</v>
+      </c>
+      <c r="D517" s="2">
+        <v>64431</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A518" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C518" s="2">
+        <v>54</v>
+      </c>
+      <c r="D518" s="2">
+        <v>60191</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A519" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C519" s="2">
+        <v>55</v>
+      </c>
+      <c r="D519" s="2">
+        <v>62965</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A520" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C520" s="2">
+        <v>56</v>
+      </c>
+      <c r="D520" s="2">
+        <v>62943</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A521" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C521" s="2">
+        <v>57</v>
+      </c>
+      <c r="D521" s="2">
+        <v>65194</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A522" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C522" s="2">
+        <v>58</v>
+      </c>
+      <c r="D522" s="2">
+        <v>62945</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A523" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C523" s="2">
+        <v>59</v>
+      </c>
+      <c r="D523" s="2">
+        <v>60722</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A524" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C524" s="2">
+        <v>60</v>
+      </c>
+      <c r="D524" s="2">
+        <v>62948</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A525" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C525" s="2">
+        <v>61</v>
+      </c>
+      <c r="D525" s="2">
+        <v>62967</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A526" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C526" s="2">
+        <v>62</v>
+      </c>
+      <c r="D526" s="2">
+        <v>64432</v>
+      </c>
+      <c r="E526" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A527" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C527" s="2">
+        <v>63</v>
+      </c>
+      <c r="D527" s="2">
+        <v>62950</v>
+      </c>
+      <c r="E527" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A528" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C528" s="2">
+        <v>64</v>
+      </c>
+      <c r="D528" s="2">
+        <v>62946</v>
+      </c>
+      <c r="E528" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A529" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C529" s="2">
+        <v>65</v>
+      </c>
+      <c r="D529" s="2">
+        <v>64433</v>
+      </c>
+      <c r="E529" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A530" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C530" s="2">
+        <v>66</v>
+      </c>
+      <c r="D530" s="2">
+        <v>62949</v>
+      </c>
+      <c r="E530" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A531" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C531" s="2">
+        <v>67</v>
+      </c>
+      <c r="D531" s="2">
+        <v>43575</v>
+      </c>
+      <c r="E531" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A532" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C532" s="2">
+        <v>101</v>
+      </c>
+      <c r="D532" s="2">
+        <v>60062</v>
+      </c>
+      <c r="E532" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A533" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C533" s="2">
+        <v>102</v>
+      </c>
+      <c r="D533" s="2">
+        <v>60063</v>
+      </c>
+      <c r="E533" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A534" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C534" s="2">
+        <v>103</v>
+      </c>
+      <c r="D534" s="2">
+        <v>60065</v>
+      </c>
+      <c r="E534" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A535" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C535" s="2">
+        <v>104</v>
+      </c>
+      <c r="D535" s="2">
+        <v>60066</v>
+      </c>
+      <c r="E535" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A536" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C536" s="2">
+        <v>105</v>
+      </c>
+      <c r="D536" s="2">
+        <v>60064</v>
+      </c>
+      <c r="E536" s="2" t="s">
+        <v>582</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E305" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E536" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/filo.xlsx
+++ b/filo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\users\i_cevik1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3B245B-E8E6-4474-8F94-576B0106AB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3359B5-B3A4-46E6-BA41-BBC78C995A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="614">
   <si>
     <t>MSN</t>
   </si>
@@ -1786,13 +1786,103 @@
   </si>
   <si>
     <t>TC-LRL</t>
+  </si>
+  <si>
+    <t>TC-LLA</t>
+  </si>
+  <si>
+    <t>TC-LLB</t>
+  </si>
+  <si>
+    <t>TC-LLC</t>
+  </si>
+  <si>
+    <t>TC-LLD</t>
+  </si>
+  <si>
+    <t>TC-LLF</t>
+  </si>
+  <si>
+    <t>TC-LLE</t>
+  </si>
+  <si>
+    <t>TC-LLG</t>
+  </si>
+  <si>
+    <t>TC-LLH</t>
+  </si>
+  <si>
+    <t>TC-LLI</t>
+  </si>
+  <si>
+    <t>TC-LLJ</t>
+  </si>
+  <si>
+    <t>TC-LLK</t>
+  </si>
+  <si>
+    <t>TC-LLM</t>
+  </si>
+  <si>
+    <t>TC-LLN</t>
+  </si>
+  <si>
+    <t>TC-LLO</t>
+  </si>
+  <si>
+    <t>TC-LLP</t>
+  </si>
+  <si>
+    <t>TC-LLU</t>
+  </si>
+  <si>
+    <t>TC-LLS</t>
+  </si>
+  <si>
+    <t>TC-LLR</t>
+  </si>
+  <si>
+    <t>TC-LLV</t>
+  </si>
+  <si>
+    <t>TC-LLT</t>
+  </si>
+  <si>
+    <t>TC-LLY</t>
+  </si>
+  <si>
+    <t>TC-LLZ</t>
+  </si>
+  <si>
+    <t>TC-LMB</t>
+  </si>
+  <si>
+    <t>TC-LMC</t>
+  </si>
+  <si>
+    <t>TC-LMD</t>
+  </si>
+  <si>
+    <t>TC-LME</t>
+  </si>
+  <si>
+    <t>TC-LMF</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>Genx-1B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General_)"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1819,6 +1909,10 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="İnherit"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Helv"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1872,8 +1966,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1893,8 +1988,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 4" xfId="1" xr:uid="{BF57FFEC-010B-41E6-9F39-1DA5913248D0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2172,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E536"/>
+  <dimension ref="A1:E563"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.6328125" style="5" customWidth="1"/>
@@ -11294,6 +11390,465 @@
         <v>582</v>
       </c>
     </row>
+    <row r="537" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A537" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C537" s="2">
+        <v>1</v>
+      </c>
+      <c r="D537" s="2">
+        <v>65801</v>
+      </c>
+      <c r="E537" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A538" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C538" s="2">
+        <v>2</v>
+      </c>
+      <c r="D538" s="2">
+        <v>65802</v>
+      </c>
+      <c r="E538" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A539" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C539" s="2">
+        <v>3</v>
+      </c>
+      <c r="D539" s="2">
+        <v>65803</v>
+      </c>
+      <c r="E539" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A540" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C540" s="2">
+        <v>4</v>
+      </c>
+      <c r="D540" s="2">
+        <v>65804</v>
+      </c>
+      <c r="E540" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A541" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C541" s="2">
+        <v>5</v>
+      </c>
+      <c r="D541" s="2">
+        <v>65806</v>
+      </c>
+      <c r="E541" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A542" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C542" s="2">
+        <v>6</v>
+      </c>
+      <c r="D542" s="2">
+        <v>65805</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A543" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C543" s="2">
+        <v>7</v>
+      </c>
+      <c r="D543" s="2">
+        <v>65807</v>
+      </c>
+      <c r="E543" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A544" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C544" s="2">
+        <v>8</v>
+      </c>
+      <c r="D544" s="2">
+        <v>65808</v>
+      </c>
+      <c r="E544" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A545" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C545" s="2">
+        <v>9</v>
+      </c>
+      <c r="D545" s="2">
+        <v>65809</v>
+      </c>
+      <c r="E545" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A546" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C546" s="2">
+        <v>10</v>
+      </c>
+      <c r="D546" s="2">
+        <v>65810</v>
+      </c>
+      <c r="E546" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A547" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C547" s="2">
+        <v>11</v>
+      </c>
+      <c r="D547" s="2">
+        <v>65811</v>
+      </c>
+      <c r="E547" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A548" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C548" s="2">
+        <v>12</v>
+      </c>
+      <c r="D548" s="2">
+        <v>65812</v>
+      </c>
+      <c r="E548" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A549" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C549" s="2">
+        <v>13</v>
+      </c>
+      <c r="D549" s="2">
+        <v>65813</v>
+      </c>
+      <c r="E549" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A550" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C550" s="2">
+        <v>14</v>
+      </c>
+      <c r="D550" s="2">
+        <v>65814</v>
+      </c>
+      <c r="E550" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A551" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C551" s="2">
+        <v>15</v>
+      </c>
+      <c r="D551" s="2">
+        <v>65815</v>
+      </c>
+      <c r="E551" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A552" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C552" s="2">
+        <v>16</v>
+      </c>
+      <c r="D552" s="2">
+        <v>65819</v>
+      </c>
+      <c r="E552" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A553" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C553" s="2">
+        <v>17</v>
+      </c>
+      <c r="D553" s="2">
+        <v>65817</v>
+      </c>
+      <c r="E553" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A554" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C554" s="2">
+        <v>18</v>
+      </c>
+      <c r="D554" s="2">
+        <v>65816</v>
+      </c>
+      <c r="E554" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A555" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C555" s="2">
+        <v>19</v>
+      </c>
+      <c r="D555" s="2">
+        <v>65820</v>
+      </c>
+      <c r="E555" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A556" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C556" s="2">
+        <v>20</v>
+      </c>
+      <c r="D556" s="2">
+        <v>65818</v>
+      </c>
+      <c r="E556" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A557" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C557" s="2">
+        <v>21</v>
+      </c>
+      <c r="D557" s="2">
+        <v>65821</v>
+      </c>
+      <c r="E557" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A558" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C558" s="2">
+        <v>22</v>
+      </c>
+      <c r="D558" s="2">
+        <v>65822</v>
+      </c>
+      <c r="E558" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A559" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C559" s="2">
+        <v>23</v>
+      </c>
+      <c r="D559" s="2">
+        <v>65823</v>
+      </c>
+      <c r="E559" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A560" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C560" s="2">
+        <v>24</v>
+      </c>
+      <c r="D560" s="2">
+        <v>65824</v>
+      </c>
+      <c r="E560" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A561" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C561" s="2">
+        <v>25</v>
+      </c>
+      <c r="D561" s="2">
+        <v>65825</v>
+      </c>
+      <c r="E561" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A562" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C562" s="2">
+        <v>26</v>
+      </c>
+      <c r="D562" s="2">
+        <v>68883</v>
+      </c>
+      <c r="E562" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A563" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C563" s="2">
+        <v>27</v>
+      </c>
+      <c r="D563" s="2">
+        <v>68884</v>
+      </c>
+      <c r="E563" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E536" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
